--- a/ranking_hover_data_combined.xlsx
+++ b/ranking_hover_data_combined.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E306"/>
+  <dimension ref="A1:E310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5219,12 +5219,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>apple2</t>
+          <t>apple1</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2025/07/23</t>
+          <t>2025/07/30</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -5233,10 +5233,10 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E209" t="n">
-        <v>201</v>
+        <v>39</v>
       </c>
     </row>
     <row r="210">
@@ -5256,7 +5256,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E210" t="n">
         <v>201</v>
@@ -5270,16 +5270,16 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2025/07/24</t>
+          <t>2025/07/23</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="E211" t="n">
         <v>201</v>
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E212" t="n">
         <v>201</v>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E213" t="n">
         <v>201</v>
@@ -5348,7 +5348,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E214" t="n">
         <v>201</v>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E215" t="n">
         <v>201</v>
@@ -5394,7 +5394,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E216" t="n">
         <v>201</v>
@@ -5408,16 +5408,16 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2025/07/25</t>
+          <t>2025/07/24</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="E217" t="n">
         <v>201</v>
@@ -5440,7 +5440,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E218" t="n">
         <v>201</v>
@@ -5463,7 +5463,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E219" t="n">
         <v>201</v>
@@ -5486,7 +5486,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E220" t="n">
         <v>201</v>
@@ -5509,7 +5509,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E221" t="n">
         <v>201</v>
@@ -5532,7 +5532,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E222" t="n">
         <v>201</v>
@@ -5555,7 +5555,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E223" t="n">
         <v>201</v>
@@ -5569,16 +5569,16 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2025/07/26</t>
+          <t>2025/07/25</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="E224" t="n">
         <v>201</v>
@@ -5601,7 +5601,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E225" t="n">
         <v>201</v>
@@ -5624,7 +5624,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E226" t="n">
         <v>201</v>
@@ -5647,7 +5647,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E227" t="n">
         <v>201</v>
@@ -5670,7 +5670,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E228" t="n">
         <v>201</v>
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E229" t="n">
         <v>201</v>
@@ -5716,7 +5716,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E230" t="n">
         <v>201</v>
@@ -5730,16 +5730,16 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2025/07/27</t>
+          <t>2025/07/26</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>土</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="E231" t="n">
         <v>201</v>
@@ -5762,7 +5762,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E232" t="n">
         <v>201</v>
@@ -5785,7 +5785,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E233" t="n">
         <v>201</v>
@@ -5808,7 +5808,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E234" t="n">
         <v>201</v>
@@ -5831,7 +5831,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E235" t="n">
         <v>201</v>
@@ -5854,7 +5854,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E236" t="n">
         <v>201</v>
@@ -5868,16 +5868,16 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2025/07/28</t>
+          <t>2025/07/27</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>日</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="E237" t="n">
         <v>201</v>
@@ -5900,7 +5900,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E238" t="n">
         <v>201</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E239" t="n">
         <v>201</v>
@@ -5946,7 +5946,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E240" t="n">
         <v>201</v>
@@ -5969,7 +5969,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E241" t="n">
         <v>201</v>
@@ -5992,7 +5992,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E242" t="n">
         <v>201</v>
@@ -6015,7 +6015,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E243" t="n">
         <v>201</v>
@@ -6029,16 +6029,16 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2025/07/29</t>
+          <t>2025/07/28</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>月</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="E244" t="n">
         <v>201</v>
@@ -6061,7 +6061,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E245" t="n">
         <v>201</v>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E246" t="n">
         <v>201</v>
@@ -6107,7 +6107,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E247" t="n">
         <v>201</v>
@@ -6130,7 +6130,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E248" t="n">
         <v>201</v>
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E249" t="n">
         <v>201</v>
@@ -6167,16 +6167,16 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2025/07/30</t>
+          <t>2025/07/29</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E250" t="n">
         <v>201</v>
@@ -6199,7 +6199,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E251" t="n">
         <v>201</v>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E252" t="n">
         <v>201</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E253" t="n">
         <v>201</v>
@@ -6268,7 +6268,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E254" t="n">
         <v>201</v>
@@ -6277,12 +6277,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>apple3</t>
+          <t>apple2</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2025/07/23</t>
+          <t>2025/07/30</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -6291,21 +6291,21 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E255" t="n">
-        <v>4</v>
+        <v>201</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>apple3</t>
+          <t>apple2</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2025/07/23</t>
+          <t>2025/07/30</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -6314,10 +6314,10 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E256" t="n">
-        <v>3</v>
+        <v>201</v>
       </c>
     </row>
     <row r="257">
@@ -6328,19 +6328,19 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2025/07/24</t>
+          <t>2025/07/23</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="D257" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E257" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="258">
@@ -6351,19 +6351,19 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2025/07/24</t>
+          <t>2025/07/23</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="E258" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="259">
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E259" t="n">
         <v>2</v>
@@ -6406,10 +6406,10 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E260" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="261">
@@ -6429,10 +6429,10 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E261" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="262">
@@ -6452,7 +6452,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E262" t="n">
         <v>4</v>
@@ -6466,16 +6466,16 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2025/07/25</t>
+          <t>2025/07/24</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E263" t="n">
         <v>4</v>
@@ -6489,16 +6489,16 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2025/07/25</t>
+          <t>2025/07/24</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E264" t="n">
         <v>4</v>
@@ -6521,7 +6521,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E265" t="n">
         <v>4</v>
@@ -6544,7 +6544,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E266" t="n">
         <v>4</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E267" t="n">
         <v>4</v>
@@ -6590,10 +6590,10 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E268" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="269">
@@ -6613,7 +6613,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E269" t="n">
         <v>4</v>
@@ -6627,19 +6627,19 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2025/07/26</t>
+          <t>2025/07/25</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E270" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="271">
@@ -6650,16 +6650,16 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2025/07/26</t>
+          <t>2025/07/25</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E271" t="n">
         <v>4</v>
@@ -6682,10 +6682,10 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E272" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="273">
@@ -6705,10 +6705,10 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E273" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="274">
@@ -6728,7 +6728,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E274" t="n">
         <v>5</v>
@@ -6751,10 +6751,10 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E275" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="276">
@@ -6774,7 +6774,7 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E276" t="n">
         <v>5</v>
@@ -6788,19 +6788,19 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2025/07/27</t>
+          <t>2025/07/26</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>土</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E277" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="278">
@@ -6811,16 +6811,16 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2025/07/27</t>
+          <t>2025/07/26</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>土</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E278" t="n">
         <v>5</v>
@@ -6843,7 +6843,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E279" t="n">
         <v>5</v>
@@ -6866,7 +6866,7 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E280" t="n">
         <v>5</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E281" t="n">
         <v>5</v>
@@ -6912,7 +6912,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E282" t="n">
         <v>5</v>
@@ -6926,16 +6926,16 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2025/07/28</t>
+          <t>2025/07/27</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>日</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E283" t="n">
         <v>5</v>
@@ -6949,16 +6949,16 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2025/07/28</t>
+          <t>2025/07/27</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>日</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="E284" t="n">
         <v>5</v>
@@ -6981,7 +6981,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E285" t="n">
         <v>5</v>
@@ -7004,7 +7004,7 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E286" t="n">
         <v>5</v>
@@ -7027,10 +7027,10 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E287" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="288">
@@ -7050,10 +7050,10 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E288" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="289">
@@ -7073,10 +7073,10 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E289" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="290">
@@ -7087,19 +7087,19 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2025/07/29</t>
+          <t>2025/07/28</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>月</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E290" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="291">
@@ -7110,16 +7110,16 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2025/07/29</t>
+          <t>2025/07/28</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>月</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E291" t="n">
         <v>5</v>
@@ -7142,10 +7142,10 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E292" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="293">
@@ -7165,7 +7165,7 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E293" t="n">
         <v>5</v>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E294" t="n">
         <v>5</v>
@@ -7211,7 +7211,7 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E295" t="n">
         <v>5</v>
@@ -7225,19 +7225,19 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2025/07/30</t>
+          <t>2025/07/29</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E296" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="297">
@@ -7248,16 +7248,16 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2025/07/30</t>
+          <t>2025/07/29</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E297" t="n">
         <v>5</v>
@@ -7280,10 +7280,10 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E298" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="299">
@@ -7303,10 +7303,10 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E299" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="300">
@@ -7326,21 +7326,21 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E300" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>spotify</t>
+          <t>apple3</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2025/07/23</t>
+          <t>2025/07/30</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -7349,56 +7349,56 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E301" t="n">
-        <v>101</v>
+        <v>4</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>spotify</t>
+          <t>apple3</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2025/07/24</t>
+          <t>2025/07/30</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E302" t="n">
-        <v>101</v>
+        <v>5</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>spotify</t>
+          <t>apple3</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2025/07/25</t>
+          <t>2025/07/30</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>水</t>
         </is>
       </c>
       <c r="D303" t="n">
         <v>21</v>
       </c>
       <c r="E303" t="n">
-        <v>101</v>
+        <v>4</v>
       </c>
     </row>
     <row r="304">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2025/07/26</t>
+          <t>2025/07/23</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>水</t>
         </is>
       </c>
       <c r="D304" t="n">
@@ -7432,12 +7432,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2025/07/27</t>
+          <t>2025/07/24</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>木</t>
         </is>
       </c>
       <c r="D305" t="n">
@@ -7455,18 +7455,110 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2025/07/28</t>
+          <t>2025/07/25</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>金</t>
         </is>
       </c>
       <c r="D306" t="n">
         <v>21</v>
       </c>
       <c r="E306" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>spotify</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>2025/07/26</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="D307" t="n">
+        <v>21</v>
+      </c>
+      <c r="E307" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>spotify</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>2025/07/27</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="D308" t="n">
+        <v>21</v>
+      </c>
+      <c r="E308" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>spotify</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="D309" t="n">
+        <v>21</v>
+      </c>
+      <c r="E309" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>spotify</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>2025/07/29</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="D310" t="n">
+        <v>21</v>
+      </c>
+      <c r="E310" t="n">
         <v>101</v>
       </c>
     </row>

--- a/ranking_hover_data_combined.xlsx
+++ b/ranking_hover_data_combined.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E310"/>
+  <dimension ref="A1:E338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5242,12 +5242,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>apple2</t>
+          <t>apple1</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2025/07/23</t>
+          <t>2025/07/30</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -5256,44 +5256,44 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E210" t="n">
-        <v>201</v>
+        <v>38</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>apple2</t>
+          <t>apple1</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2025/07/23</t>
+          <t>2025/07/31</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>木</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="E211" t="n">
-        <v>201</v>
+        <v>39</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>apple2</t>
+          <t>apple1</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2025/07/24</t>
+          <t>2025/07/31</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -5302,21 +5302,21 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E212" t="n">
-        <v>201</v>
+        <v>38</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>apple2</t>
+          <t>apple1</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2025/07/24</t>
+          <t>2025/07/31</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -5325,21 +5325,21 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E213" t="n">
-        <v>201</v>
+        <v>38</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>apple2</t>
+          <t>apple1</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2025/07/24</t>
+          <t>2025/07/31</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -5348,21 +5348,21 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E214" t="n">
-        <v>201</v>
+        <v>31</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>apple2</t>
+          <t>apple1</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2025/07/24</t>
+          <t>2025/07/31</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -5371,21 +5371,21 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E215" t="n">
-        <v>201</v>
+        <v>31</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>apple2</t>
+          <t>apple1</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2025/07/24</t>
+          <t>2025/07/31</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -5397,41 +5397,41 @@
         <v>20</v>
       </c>
       <c r="E216" t="n">
-        <v>201</v>
+        <v>32</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>apple2</t>
+          <t>apple1</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2025/07/24</t>
+          <t>2025/08/01</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>金</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E217" t="n">
-        <v>201</v>
+        <v>34</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>apple2</t>
+          <t>apple1</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2025/07/25</t>
+          <t>2025/08/01</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -5440,10 +5440,10 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E218" t="n">
-        <v>201</v>
+        <v>40</v>
       </c>
     </row>
     <row r="219">
@@ -5454,16 +5454,16 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2025/07/25</t>
+          <t>2025/07/23</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>水</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E219" t="n">
         <v>201</v>
@@ -5477,16 +5477,16 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2025/07/25</t>
+          <t>2025/07/23</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>水</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E220" t="n">
         <v>201</v>
@@ -5500,16 +5500,16 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2025/07/25</t>
+          <t>2025/07/24</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E221" t="n">
         <v>201</v>
@@ -5523,16 +5523,16 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2025/07/25</t>
+          <t>2025/07/24</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E222" t="n">
         <v>201</v>
@@ -5546,16 +5546,16 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2025/07/25</t>
+          <t>2025/07/24</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E223" t="n">
         <v>201</v>
@@ -5569,16 +5569,16 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2025/07/25</t>
+          <t>2025/07/24</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E224" t="n">
         <v>201</v>
@@ -5592,16 +5592,16 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2025/07/26</t>
+          <t>2025/07/24</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>木</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E225" t="n">
         <v>201</v>
@@ -5615,16 +5615,16 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2025/07/26</t>
+          <t>2025/07/24</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>木</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E226" t="n">
         <v>201</v>
@@ -5638,16 +5638,16 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2025/07/26</t>
+          <t>2025/07/25</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E227" t="n">
         <v>201</v>
@@ -5661,16 +5661,16 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2025/07/26</t>
+          <t>2025/07/25</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E228" t="n">
         <v>201</v>
@@ -5684,16 +5684,16 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2025/07/26</t>
+          <t>2025/07/25</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E229" t="n">
         <v>201</v>
@@ -5707,16 +5707,16 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2025/07/26</t>
+          <t>2025/07/25</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E230" t="n">
         <v>201</v>
@@ -5730,16 +5730,16 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2025/07/26</t>
+          <t>2025/07/25</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E231" t="n">
         <v>201</v>
@@ -5753,16 +5753,16 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2025/07/27</t>
+          <t>2025/07/25</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>金</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E232" t="n">
         <v>201</v>
@@ -5776,16 +5776,16 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2025/07/27</t>
+          <t>2025/07/25</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>金</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E233" t="n">
         <v>201</v>
@@ -5799,16 +5799,16 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2025/07/27</t>
+          <t>2025/07/26</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>土</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E234" t="n">
         <v>201</v>
@@ -5822,16 +5822,16 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2025/07/27</t>
+          <t>2025/07/26</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>土</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E235" t="n">
         <v>201</v>
@@ -5845,16 +5845,16 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2025/07/27</t>
+          <t>2025/07/26</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>土</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E236" t="n">
         <v>201</v>
@@ -5868,16 +5868,16 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2025/07/27</t>
+          <t>2025/07/26</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>土</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E237" t="n">
         <v>201</v>
@@ -5891,16 +5891,16 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2025/07/28</t>
+          <t>2025/07/26</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>土</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E238" t="n">
         <v>201</v>
@@ -5914,16 +5914,16 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2025/07/28</t>
+          <t>2025/07/26</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>土</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E239" t="n">
         <v>201</v>
@@ -5937,16 +5937,16 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2025/07/28</t>
+          <t>2025/07/26</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>土</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E240" t="n">
         <v>201</v>
@@ -5960,16 +5960,16 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2025/07/28</t>
+          <t>2025/07/27</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>日</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E241" t="n">
         <v>201</v>
@@ -5983,16 +5983,16 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2025/07/28</t>
+          <t>2025/07/27</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>日</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E242" t="n">
         <v>201</v>
@@ -6006,16 +6006,16 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2025/07/28</t>
+          <t>2025/07/27</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>日</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E243" t="n">
         <v>201</v>
@@ -6029,16 +6029,16 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2025/07/28</t>
+          <t>2025/07/27</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>日</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E244" t="n">
         <v>201</v>
@@ -6052,16 +6052,16 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2025/07/29</t>
+          <t>2025/07/27</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>日</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E245" t="n">
         <v>201</v>
@@ -6075,16 +6075,16 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2025/07/29</t>
+          <t>2025/07/27</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>日</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E246" t="n">
         <v>201</v>
@@ -6098,16 +6098,16 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2025/07/29</t>
+          <t>2025/07/28</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>月</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E247" t="n">
         <v>201</v>
@@ -6121,16 +6121,16 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2025/07/29</t>
+          <t>2025/07/28</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>月</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E248" t="n">
         <v>201</v>
@@ -6144,16 +6144,16 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2025/07/29</t>
+          <t>2025/07/28</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>月</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E249" t="n">
         <v>201</v>
@@ -6167,16 +6167,16 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2025/07/29</t>
+          <t>2025/07/28</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>月</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E250" t="n">
         <v>201</v>
@@ -6190,16 +6190,16 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2025/07/30</t>
+          <t>2025/07/28</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>月</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E251" t="n">
         <v>201</v>
@@ -6213,16 +6213,16 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2025/07/30</t>
+          <t>2025/07/28</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>月</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E252" t="n">
         <v>201</v>
@@ -6236,16 +6236,16 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2025/07/30</t>
+          <t>2025/07/28</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>月</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E253" t="n">
         <v>201</v>
@@ -6259,16 +6259,16 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2025/07/30</t>
+          <t>2025/07/29</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E254" t="n">
         <v>201</v>
@@ -6282,16 +6282,16 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2025/07/30</t>
+          <t>2025/07/29</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="D255" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E255" t="n">
         <v>201</v>
@@ -6305,16 +6305,16 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2025/07/30</t>
+          <t>2025/07/29</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E256" t="n">
         <v>201</v>
@@ -6323,415 +6323,415 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>apple3</t>
+          <t>apple2</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2025/07/23</t>
+          <t>2025/07/29</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="D257" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E257" t="n">
-        <v>4</v>
+        <v>201</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>apple3</t>
+          <t>apple2</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2025/07/23</t>
+          <t>2025/07/29</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E258" t="n">
-        <v>3</v>
+        <v>201</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>apple3</t>
+          <t>apple2</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2025/07/24</t>
+          <t>2025/07/29</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>火</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E259" t="n">
-        <v>2</v>
+        <v>201</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>apple3</t>
+          <t>apple2</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2025/07/24</t>
+          <t>2025/07/30</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="D260" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E260" t="n">
-        <v>2</v>
+        <v>201</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>apple3</t>
+          <t>apple2</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2025/07/24</t>
+          <t>2025/07/30</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="D261" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E261" t="n">
-        <v>2</v>
+        <v>201</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>apple3</t>
+          <t>apple2</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2025/07/24</t>
+          <t>2025/07/30</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E262" t="n">
-        <v>4</v>
+        <v>201</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>apple3</t>
+          <t>apple2</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2025/07/24</t>
+          <t>2025/07/30</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E263" t="n">
-        <v>4</v>
+        <v>201</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>apple3</t>
+          <t>apple2</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2025/07/24</t>
+          <t>2025/07/30</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E264" t="n">
-        <v>4</v>
+        <v>201</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>apple3</t>
+          <t>apple2</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2025/07/25</t>
+          <t>2025/07/30</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>水</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="E265" t="n">
-        <v>4</v>
+        <v>201</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>apple3</t>
+          <t>apple2</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2025/07/25</t>
+          <t>2025/07/30</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>水</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E266" t="n">
-        <v>4</v>
+        <v>201</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>apple3</t>
+          <t>apple2</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2025/07/25</t>
+          <t>2025/07/31</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E267" t="n">
-        <v>4</v>
+        <v>201</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>apple3</t>
+          <t>apple2</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2025/07/25</t>
+          <t>2025/07/31</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E268" t="n">
-        <v>4</v>
+        <v>201</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>apple3</t>
+          <t>apple2</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2025/07/25</t>
+          <t>2025/07/31</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E269" t="n">
-        <v>4</v>
+        <v>201</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>apple3</t>
+          <t>apple2</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2025/07/25</t>
+          <t>2025/07/31</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E270" t="n">
-        <v>5</v>
+        <v>201</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>apple3</t>
+          <t>apple2</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2025/07/25</t>
+          <t>2025/07/31</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E271" t="n">
-        <v>4</v>
+        <v>201</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>apple3</t>
+          <t>apple2</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2025/07/26</t>
+          <t>2025/07/31</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>木</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E272" t="n">
-        <v>4</v>
+        <v>201</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>apple3</t>
+          <t>apple2</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2025/07/26</t>
+          <t>2025/07/31</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>木</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E273" t="n">
-        <v>4</v>
+        <v>201</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>apple3</t>
+          <t>apple2</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2025/07/26</t>
+          <t>2025/08/01</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="D274" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E274" t="n">
-        <v>5</v>
+        <v>201</v>
       </c>
     </row>
     <row r="275">
@@ -6742,19 +6742,19 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2025/07/26</t>
+          <t>2025/07/23</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>水</t>
         </is>
       </c>
       <c r="D275" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E275" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="276">
@@ -6765,19 +6765,19 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2025/07/26</t>
+          <t>2025/07/23</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>水</t>
         </is>
       </c>
       <c r="D276" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E276" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="277">
@@ -6788,19 +6788,19 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2025/07/26</t>
+          <t>2025/07/24</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>木</t>
         </is>
       </c>
       <c r="D277" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E277" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="278">
@@ -6811,19 +6811,19 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2025/07/26</t>
+          <t>2025/07/24</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>木</t>
         </is>
       </c>
       <c r="D278" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="E278" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="279">
@@ -6834,19 +6834,19 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2025/07/27</t>
+          <t>2025/07/24</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>木</t>
         </is>
       </c>
       <c r="D279" t="n">
+        <v>9</v>
+      </c>
+      <c r="E279" t="n">
         <v>2</v>
-      </c>
-      <c r="E279" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="280">
@@ -6857,19 +6857,19 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2025/07/27</t>
+          <t>2025/07/24</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>木</t>
         </is>
       </c>
       <c r="D280" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E280" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="281">
@@ -6880,19 +6880,19 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2025/07/27</t>
+          <t>2025/07/24</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>木</t>
         </is>
       </c>
       <c r="D281" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E281" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="282">
@@ -6903,19 +6903,19 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2025/07/27</t>
+          <t>2025/07/24</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>木</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E282" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="283">
@@ -6926,19 +6926,19 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2025/07/27</t>
+          <t>2025/07/25</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>金</t>
         </is>
       </c>
       <c r="D283" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E283" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="284">
@@ -6949,19 +6949,19 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2025/07/27</t>
+          <t>2025/07/25</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>金</t>
         </is>
       </c>
       <c r="D284" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="E284" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="285">
@@ -6972,19 +6972,19 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2025/07/28</t>
+          <t>2025/07/25</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>金</t>
         </is>
       </c>
       <c r="D285" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E285" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="286">
@@ -6995,19 +6995,19 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2025/07/28</t>
+          <t>2025/07/25</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>金</t>
         </is>
       </c>
       <c r="D286" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E286" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="287">
@@ -7018,19 +7018,19 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2025/07/28</t>
+          <t>2025/07/25</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>金</t>
         </is>
       </c>
       <c r="D287" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E287" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="288">
@@ -7041,16 +7041,16 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2025/07/28</t>
+          <t>2025/07/25</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>金</t>
         </is>
       </c>
       <c r="D288" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E288" t="n">
         <v>5</v>
@@ -7064,16 +7064,16 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2025/07/28</t>
+          <t>2025/07/25</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>金</t>
         </is>
       </c>
       <c r="D289" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E289" t="n">
         <v>4</v>
@@ -7087,16 +7087,16 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2025/07/28</t>
+          <t>2025/07/26</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>土</t>
         </is>
       </c>
       <c r="D290" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E290" t="n">
         <v>4</v>
@@ -7110,19 +7110,19 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2025/07/28</t>
+          <t>2025/07/26</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>土</t>
         </is>
       </c>
       <c r="D291" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="E291" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="292">
@@ -7133,19 +7133,19 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2025/07/29</t>
+          <t>2025/07/26</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>土</t>
         </is>
       </c>
       <c r="D292" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E292" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="293">
@@ -7156,16 +7156,16 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2025/07/29</t>
+          <t>2025/07/26</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>土</t>
         </is>
       </c>
       <c r="D293" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E293" t="n">
         <v>5</v>
@@ -7179,16 +7179,16 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2025/07/29</t>
+          <t>2025/07/26</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>土</t>
         </is>
       </c>
       <c r="D294" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E294" t="n">
         <v>5</v>
@@ -7202,19 +7202,19 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2025/07/29</t>
+          <t>2025/07/26</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>土</t>
         </is>
       </c>
       <c r="D295" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E295" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="296">
@@ -7225,16 +7225,16 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2025/07/29</t>
+          <t>2025/07/26</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>土</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E296" t="n">
         <v>5</v>
@@ -7248,16 +7248,16 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2025/07/29</t>
+          <t>2025/07/27</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>日</t>
         </is>
       </c>
       <c r="D297" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E297" t="n">
         <v>5</v>
@@ -7271,19 +7271,19 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2025/07/30</t>
+          <t>2025/07/27</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>日</t>
         </is>
       </c>
       <c r="D298" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E298" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="299">
@@ -7294,16 +7294,16 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2025/07/30</t>
+          <t>2025/07/27</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>日</t>
         </is>
       </c>
       <c r="D299" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E299" t="n">
         <v>5</v>
@@ -7317,19 +7317,19 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2025/07/30</t>
+          <t>2025/07/27</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>日</t>
         </is>
       </c>
       <c r="D300" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E300" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="301">
@@ -7340,19 +7340,19 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2025/07/30</t>
+          <t>2025/07/27</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>日</t>
         </is>
       </c>
       <c r="D301" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E301" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="302">
@@ -7363,16 +7363,16 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2025/07/30</t>
+          <t>2025/07/27</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>日</t>
         </is>
       </c>
       <c r="D302" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E302" t="n">
         <v>5</v>
@@ -7386,140 +7386,140 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2025/07/30</t>
+          <t>2025/07/28</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>月</t>
         </is>
       </c>
       <c r="D303" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="E303" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>spotify</t>
+          <t>apple3</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2025/07/23</t>
+          <t>2025/07/28</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>月</t>
         </is>
       </c>
       <c r="D304" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E304" t="n">
-        <v>101</v>
+        <v>5</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>spotify</t>
+          <t>apple3</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2025/07/24</t>
+          <t>2025/07/28</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>月</t>
         </is>
       </c>
       <c r="D305" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E305" t="n">
-        <v>101</v>
+        <v>5</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>spotify</t>
+          <t>apple3</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2025/07/25</t>
+          <t>2025/07/28</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>月</t>
         </is>
       </c>
       <c r="D306" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E306" t="n">
-        <v>101</v>
+        <v>5</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>spotify</t>
+          <t>apple3</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2025/07/26</t>
+          <t>2025/07/28</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>月</t>
         </is>
       </c>
       <c r="D307" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E307" t="n">
-        <v>101</v>
+        <v>4</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>spotify</t>
+          <t>apple3</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2025/07/27</t>
+          <t>2025/07/28</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>日</t>
+          <t>月</t>
         </is>
       </c>
       <c r="D308" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E308" t="n">
-        <v>101</v>
+        <v>4</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>spotify</t>
+          <t>apple3</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -7533,32 +7533,676 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E309" t="n">
-        <v>101</v>
+        <v>5</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
+          <t>apple3</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>2025/07/29</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="D310" t="n">
+        <v>2</v>
+      </c>
+      <c r="E310" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>apple3</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>2025/07/29</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="D311" t="n">
+        <v>6</v>
+      </c>
+      <c r="E311" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>apple3</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>2025/07/29</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="D312" t="n">
+        <v>8</v>
+      </c>
+      <c r="E312" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>apple3</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>2025/07/29</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="D313" t="n">
+        <v>14</v>
+      </c>
+      <c r="E313" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>apple3</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>2025/07/29</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="D314" t="n">
+        <v>18</v>
+      </c>
+      <c r="E314" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>apple3</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>2025/07/29</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="D315" t="n">
+        <v>20</v>
+      </c>
+      <c r="E315" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>apple3</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>2025/07/30</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="D316" t="n">
+        <v>0</v>
+      </c>
+      <c r="E316" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>apple3</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>2025/07/30</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="D317" t="n">
+        <v>2</v>
+      </c>
+      <c r="E317" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>apple3</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>2025/07/30</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="D318" t="n">
+        <v>6</v>
+      </c>
+      <c r="E318" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>apple3</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>2025/07/30</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="D319" t="n">
+        <v>8</v>
+      </c>
+      <c r="E319" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>apple3</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>2025/07/30</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="D320" t="n">
+        <v>15</v>
+      </c>
+      <c r="E320" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>apple3</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>2025/07/30</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="D321" t="n">
+        <v>21</v>
+      </c>
+      <c r="E321" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>apple3</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>2025/07/30</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="D322" t="n">
+        <v>23</v>
+      </c>
+      <c r="E322" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>apple3</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>2025/07/31</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="D323" t="n">
+        <v>2</v>
+      </c>
+      <c r="E323" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>apple3</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>2025/07/31</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="D324" t="n">
+        <v>6</v>
+      </c>
+      <c r="E324" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>apple3</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>2025/07/31</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="D325" t="n">
+        <v>8</v>
+      </c>
+      <c r="E325" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>apple3</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>2025/07/31</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="D326" t="n">
+        <v>14</v>
+      </c>
+      <c r="E326" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>apple3</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>2025/07/31</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="D327" t="n">
+        <v>18</v>
+      </c>
+      <c r="E327" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>apple3</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>2025/07/31</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="D328" t="n">
+        <v>20</v>
+      </c>
+      <c r="E328" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>apple3</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>2025/07/31</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="D329" t="n">
+        <v>23</v>
+      </c>
+      <c r="E329" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>apple3</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>2025/08/01</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="D330" t="n">
+        <v>3</v>
+      </c>
+      <c r="E330" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
           <t>spotify</t>
         </is>
       </c>
-      <c r="B310" t="inlineStr">
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>2025/07/23</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="D331" t="n">
+        <v>21</v>
+      </c>
+      <c r="E331" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>spotify</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>2025/07/24</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="D332" t="n">
+        <v>21</v>
+      </c>
+      <c r="E332" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>spotify</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>2025/07/25</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="D333" t="n">
+        <v>21</v>
+      </c>
+      <c r="E333" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>spotify</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>2025/07/26</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="D334" t="n">
+        <v>21</v>
+      </c>
+      <c r="E334" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>spotify</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>2025/07/27</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="D335" t="n">
+        <v>21</v>
+      </c>
+      <c r="E335" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>spotify</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="D336" t="n">
+        <v>21</v>
+      </c>
+      <c r="E336" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>spotify</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
         <is>
           <t>2025/07/29</t>
         </is>
       </c>
-      <c r="C310" t="inlineStr">
+      <c r="C337" t="inlineStr">
         <is>
           <t>火</t>
         </is>
       </c>
-      <c r="D310" t="n">
+      <c r="D337" t="n">
         <v>21</v>
       </c>
-      <c r="E310" t="n">
+      <c r="E337" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>spotify</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>2025/07/30</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="D338" t="n">
+        <v>21</v>
+      </c>
+      <c r="E338" t="n">
         <v>101</v>
       </c>
     </row>
